--- a/output/pdf_financials_xlsx/ADYA.xlsx
+++ b/output/pdf_financials_xlsx/ADYA.xlsx
@@ -7703,13 +7703,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.016991</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.016526</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.015242</v>
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
@@ -7740,22 +7740,22 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.07105499999999999</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.270542</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.273818</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.249002</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.196624</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.197338</v>
       </c>
     </row>
     <row r="125">
@@ -7765,13 +7765,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.016991</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.016526</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.015242</v>
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
@@ -7802,22 +7802,22 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.07105499999999999</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.270542</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.273818</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.249002</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.196624</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.197338</v>
       </c>
     </row>
     <row r="126">
@@ -24351,7 +24351,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -33902,7 +33906,11 @@
           <t>Capital lease payments</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E259" s="5" t="n">
         <v>-0.016991</v>
       </c>

--- a/output/pdf_financials_xlsx/ADYA.xlsx
+++ b/output/pdf_financials_xlsx/ADYA.xlsx
@@ -6979,7 +6979,7 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -31096,7 +31096,11 @@
           <t>Proceeds on disposal of property and equipment 8</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
